--- a/output/StructureDefinition-BRPrescricaoMedicamento.xlsx
+++ b/output/StructureDefinition-BRPrescricaoMedicamento.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T11:16:11-03:00</t>
+    <t>2026-08-24T11:43:54-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-BRPrescricaoMedicamento.xlsx
+++ b/output/StructureDefinition-BRPrescricaoMedicamento.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-24T11:43:54-03:00</t>
+    <t>2026-09-15T15:40:41-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-BRPrescricaoMedicamento.xlsx
+++ b/output/StructureDefinition-BRPrescricaoMedicamento.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T15:40:41-03:00</t>
+    <t>2026-09-23T09:07:03-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-BRPrescricaoMedicamento.xlsx
+++ b/output/StructureDefinition-BRPrescricaoMedicamento.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T09:07:03-03:00</t>
+    <t>2026-09-30T18:22:16-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-BRPrescricaoMedicamento.xlsx
+++ b/output/StructureDefinition-BRPrescricaoMedicamento.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T18:22:16-03:00</t>
+    <t>2026-10-06T15:47:25-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-BRPrescricaoMedicamento.xlsx
+++ b/output/StructureDefinition-BRPrescricaoMedicamento.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7637" uniqueCount="996">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7637" uniqueCount="997">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T15:47:25-03:00</t>
+    <t>2026-10-07T20:38:46-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1710,6 +1710,12 @@
     <t>periodUnit</t>
   </si>
   <si>
+    <t>Define a unidade de tempo segundo o UCUM</t>
+  </si>
+  <si>
+    <t>http://www.saude.gov.br/fhir/r4/ValueSet/BRUnidadeTempo</t>
+  </si>
+  <si>
     <t>MedicationRequest.dosageInstruction.timing.repeat.extension:period.extension:periodUnit.id</t>
   </si>
   <si>
@@ -1750,12 +1756,6 @@
   </si>
   <si>
     <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
-  </si>
-  <si>
-    <t>Define a unidade de tempo segundo o UCUM</t>
-  </si>
-  <si>
-    <t>http://www.saude.gov.br/fhir/r4/ValueSet/BRUnidadeTempo</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -2709,6 +2709,10 @@
   </si>
   <si>
     <t>Dosage.maxDosePerAdministration</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>not supported</t>
@@ -14826,13 +14830,13 @@
         <v>81</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>81</v>
+        <v>161</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>81</v>
+        <v>543</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>81</v>
+        <v>544</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>81</v>
@@ -14882,10 +14886,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14997,10 +15001,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15114,10 +15118,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15143,13 +15147,13 @@
         <v>104</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -15199,7 +15203,7 @@
         <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>90</v>
@@ -15231,10 +15235,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15260,10 +15264,10 @@
         <v>110</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -15293,10 +15297,10 @@
         <v>161</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>557</v>
+        <v>543</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>81</v>
@@ -15813,7 +15817,7 @@
         <v>572</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15928,7 +15932,7 @@
         <v>573</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16045,7 +16049,7 @@
         <v>574</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16071,13 +16075,13 @@
         <v>104</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -16127,7 +16131,7 @@
         <v>81</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>90</v>
@@ -16162,7 +16166,7 @@
         <v>575</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16191,7 +16195,7 @@
         <v>571</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -16303,13 +16307,13 @@
         <v>104</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -16359,7 +16363,7 @@
         <v>81</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>90</v>
@@ -16420,10 +16424,10 @@
         <v>582</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -16884,13 +16888,13 @@
         <v>104</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -16940,7 +16944,7 @@
         <v>81</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>90</v>
@@ -22802,7 +22806,7 @@
         <v>81</v>
       </c>
       <c r="AJ166" t="s" s="2">
-        <v>102</v>
+        <v>872</v>
       </c>
       <c r="AK166" t="s" s="2">
         <v>81</v>
@@ -22811,7 +22815,7 @@
         <v>81</v>
       </c>
       <c r="AM166" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="AN166" t="s" s="2">
         <v>81</v>
@@ -22822,10 +22826,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22937,10 +22941,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -23054,10 +23058,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -23173,10 +23177,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23205,7 +23209,7 @@
         <v>818</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="N170" s="2"/>
       <c r="O170" t="s" s="2">
@@ -23292,10 +23296,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23409,10 +23413,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23526,10 +23530,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23645,10 +23649,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23674,14 +23678,14 @@
         <v>866</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="N174" s="2"/>
       <c r="O174" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="P174" t="s" s="2">
         <v>81</v>
@@ -23730,7 +23734,7 @@
         <v>81</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>79</v>
@@ -23742,7 +23746,7 @@
         <v>81</v>
       </c>
       <c r="AJ174" t="s" s="2">
-        <v>102</v>
+        <v>872</v>
       </c>
       <c r="AK174" t="s" s="2">
         <v>81</v>
@@ -23751,7 +23755,7 @@
         <v>81</v>
       </c>
       <c r="AM174" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="AN174" t="s" s="2">
         <v>81</v>
@@ -23762,10 +23766,10 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23788,13 +23792,13 @@
         <v>81</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="N175" s="2"/>
       <c r="O175" s="2"/>
@@ -23845,7 +23849,7 @@
         <v>81</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>79</v>
@@ -23863,10 +23867,10 @@
         <v>81</v>
       </c>
       <c r="AL175" t="s" s="2">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="AM175" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="AN175" t="s" s="2">
         <v>81</v>
@@ -23877,10 +23881,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23992,10 +23996,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -24109,10 +24113,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24228,10 +24232,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -24254,16 +24258,16 @@
         <v>81</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="N179" t="s" s="2">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="O179" s="2"/>
       <c r="P179" t="s" s="2">
@@ -24313,7 +24317,7 @@
         <v>81</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>79</v>
@@ -24334,7 +24338,7 @@
         <v>81</v>
       </c>
       <c r="AM179" t="s" s="2">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="AN179" t="s" s="2">
         <v>81</v>
@@ -24345,10 +24349,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24460,10 +24464,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24577,10 +24581,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24696,10 +24700,10 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24725,10 +24729,10 @@
         <v>866</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="N183" s="2"/>
       <c r="O183" s="2"/>
@@ -24779,7 +24783,7 @@
         <v>81</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>79</v>
@@ -24791,7 +24795,7 @@
         <v>81</v>
       </c>
       <c r="AJ183" t="s" s="2">
-        <v>102</v>
+        <v>872</v>
       </c>
       <c r="AK183" t="s" s="2">
         <v>81</v>
@@ -24800,7 +24804,7 @@
         <v>81</v>
       </c>
       <c r="AM183" t="s" s="2">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="AN183" t="s" s="2">
         <v>81</v>
@@ -24811,10 +24815,10 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24837,13 +24841,13 @@
         <v>81</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="N184" s="2"/>
       <c r="O184" s="2"/>
@@ -24894,7 +24898,7 @@
         <v>81</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>79</v>
@@ -24915,7 +24919,7 @@
         <v>81</v>
       </c>
       <c r="AM184" t="s" s="2">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="AN184" t="s" s="2">
         <v>81</v>
@@ -24926,10 +24930,10 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24952,10 +24956,10 @@
         <v>81</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="M185" t="s" s="2">
         <v>641</v>
@@ -25009,7 +25013,7 @@
         <v>81</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>79</v>
@@ -25030,7 +25034,7 @@
         <v>81</v>
       </c>
       <c r="AM185" t="s" s="2">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="AN185" t="s" s="2">
         <v>81</v>
@@ -25041,10 +25045,10 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -25070,16 +25074,16 @@
         <v>306</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="N186" t="s" s="2">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="O186" t="s" s="2">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="P186" t="s" s="2">
         <v>81</v>
@@ -25128,7 +25132,7 @@
         <v>81</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>79</v>
@@ -25146,10 +25150,10 @@
         <v>81</v>
       </c>
       <c r="AL186" t="s" s="2">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="AM186" t="s" s="2">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="AN186" t="s" s="2">
         <v>81</v>
@@ -25160,10 +25164,10 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -25189,13 +25193,13 @@
         <v>678</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="N187" t="s" s="2">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="O187" s="2"/>
       <c r="P187" t="s" s="2">
@@ -25245,7 +25249,7 @@
         <v>81</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>79</v>
@@ -25263,24 +25267,24 @@
         <v>81</v>
       </c>
       <c r="AL187" t="s" s="2">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="AM187" t="s" s="2">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="AN187" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO187" t="s" s="2">
-        <v>927</v>
+        <v>928</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -25306,10 +25310,10 @@
         <v>866</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="N188" s="2"/>
       <c r="O188" s="2"/>
@@ -25360,7 +25364,7 @@
         <v>81</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>79</v>
@@ -25372,30 +25376,30 @@
         <v>81</v>
       </c>
       <c r="AJ188" t="s" s="2">
-        <v>102</v>
+        <v>872</v>
       </c>
       <c r="AK188" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL188" t="s" s="2">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="AM188" t="s" s="2">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="AN188" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO188" t="s" s="2">
-        <v>933</v>
+        <v>934</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -25507,10 +25511,10 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -25624,10 +25628,10 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -25743,10 +25747,10 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -25775,7 +25779,7 @@
         <v>818</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="N192" s="2"/>
       <c r="O192" t="s" s="2">
@@ -25862,10 +25866,10 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -25979,10 +25983,10 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -26096,10 +26100,10 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -26215,10 +26219,10 @@
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -26241,16 +26245,16 @@
         <v>81</v>
       </c>
       <c r="K196" t="s" s="2">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="N196" t="s" s="2">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="O196" s="2"/>
       <c r="P196" t="s" s="2">
@@ -26300,7 +26304,7 @@
         <v>81</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>79</v>
@@ -26318,10 +26322,10 @@
         <v>81</v>
       </c>
       <c r="AL196" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="AM196" t="s" s="2">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="AN196" t="s" s="2">
         <v>81</v>
@@ -26332,10 +26336,10 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -26361,10 +26365,10 @@
         <v>313</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="N197" s="2"/>
       <c r="O197" s="2"/>
@@ -26415,7 +26419,7 @@
         <v>81</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>79</v>
@@ -26436,7 +26440,7 @@
         <v>81</v>
       </c>
       <c r="AM197" t="s" s="2">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="AN197" t="s" s="2">
         <v>389</v>
@@ -26447,10 +26451,10 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -26473,13 +26477,13 @@
         <v>81</v>
       </c>
       <c r="K198" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="N198" s="2"/>
       <c r="O198" s="2"/>
@@ -26530,7 +26534,7 @@
         <v>81</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>79</v>
@@ -26548,10 +26552,10 @@
         <v>81</v>
       </c>
       <c r="AL198" t="s" s="2">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="AM198" t="s" s="2">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="AN198" t="s" s="2">
         <v>81</v>
@@ -26562,10 +26566,10 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -26677,10 +26681,10 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -26794,10 +26798,10 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -26913,10 +26917,10 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -26939,16 +26943,16 @@
         <v>81</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="N202" t="s" s="2">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="O202" s="2"/>
       <c r="P202" t="s" s="2">
@@ -26977,10 +26981,10 @@
         <v>173</v>
       </c>
       <c r="Y202" t="s" s="2">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="Z202" t="s" s="2">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="AA202" t="s" s="2">
         <v>81</v>
@@ -26998,7 +27002,7 @@
         <v>81</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>90</v>
@@ -27016,24 +27020,24 @@
         <v>81</v>
       </c>
       <c r="AL202" t="s" s="2">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="AM202" t="s" s="2">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="AN202" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO202" t="s" s="2">
-        <v>967</v>
+        <v>968</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -27059,10 +27063,10 @@
         <v>169</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="N203" s="2"/>
       <c r="O203" s="2"/>
@@ -27092,10 +27096,10 @@
         <v>173</v>
       </c>
       <c r="Y203" t="s" s="2">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="Z203" t="s" s="2">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="AA203" t="s" s="2">
         <v>81</v>
@@ -27113,7 +27117,7 @@
         <v>81</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>79</v>
@@ -27131,24 +27135,24 @@
         <v>81</v>
       </c>
       <c r="AL203" t="s" s="2">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="AM203" t="s" s="2">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="AN203" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO203" t="s" s="2">
-        <v>975</v>
+        <v>976</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -27171,13 +27175,13 @@
         <v>81</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="N204" s="2"/>
       <c r="O204" s="2"/>
@@ -27228,7 +27232,7 @@
         <v>81</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>79</v>
@@ -27243,13 +27247,13 @@
         <v>102</v>
       </c>
       <c r="AK204" t="s" s="2">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="AL204" t="s" s="2">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="AM204" t="s" s="2">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="AN204" t="s" s="2">
         <v>81</v>
@@ -27260,14 +27264,14 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="E205" s="2"/>
       <c r="F205" t="s" s="2">
@@ -27286,16 +27290,16 @@
         <v>81</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="N205" t="s" s="2">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="O205" s="2"/>
       <c r="P205" t="s" s="2">
@@ -27345,7 +27349,7 @@
         <v>81</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>79</v>
@@ -27366,7 +27370,7 @@
         <v>81</v>
       </c>
       <c r="AM205" t="s" s="2">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="AN205" t="s" s="2">
         <v>81</v>
@@ -27377,10 +27381,10 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -27403,16 +27407,16 @@
         <v>81</v>
       </c>
       <c r="K206" t="s" s="2">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="N206" t="s" s="2">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="O206" s="2"/>
       <c r="P206" t="s" s="2">
@@ -27462,7 +27466,7 @@
         <v>81</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>79</v>
@@ -27477,13 +27481,13 @@
         <v>102</v>
       </c>
       <c r="AK206" t="s" s="2">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="AL206" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM206" t="s" s="2">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="AN206" t="s" s="2">
         <v>81</v>

--- a/output/StructureDefinition-BRPrescricaoMedicamento.xlsx
+++ b/output/StructureDefinition-BRPrescricaoMedicamento.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T20:38:46-03:00</t>
+    <t>2026-10-08T20:36:58-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-BRPrescricaoMedicamento.xlsx
+++ b/output/StructureDefinition-BRPrescricaoMedicamento.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T20:36:58-03:00</t>
+    <t>2026-10-14T17:05:02-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-BRPrescricaoMedicamento.xlsx
+++ b/output/StructureDefinition-BRPrescricaoMedicamento.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T17:05:02-03:00</t>
+    <t>2026-10-19T10:41:45-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-BRPrescricaoMedicamento.xlsx
+++ b/output/StructureDefinition-BRPrescricaoMedicamento.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T10:41:45-03:00</t>
+    <t>2026-10-20T16:57:20-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-BRPrescricaoMedicamento.xlsx
+++ b/output/StructureDefinition-BRPrescricaoMedicamento.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T16:57:20-03:00</t>
+    <t>2026-10-21T08:58:18-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-BRPrescricaoMedicamento.xlsx
+++ b/output/StructureDefinition-BRPrescricaoMedicamento.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T08:58:18-03:00</t>
+    <t>2026-10-21T11:27:45-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-BRPrescricaoMedicamento.xlsx
+++ b/output/StructureDefinition-BRPrescricaoMedicamento.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T11:27:45-03:00</t>
+    <t>2026-10-21T12:30:11-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
